--- a/docs/proposals/softbank-ultraman-caravan/SB様提示用_月別ライン供給計画_27ヶ月版.xlsx
+++ b/docs/proposals/softbank-ultraman-caravan/SB様提示用_月別ライン供給計画_27ヶ月版.xlsx
@@ -1093,25 +1093,25 @@
         </is>
       </c>
       <c r="B20" s="9" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C20" s="9" t="n">
         <v>15</v>
       </c>
       <c r="D20" s="10" t="n">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="E20" s="10" t="n">
-        <v>12000000</v>
+        <v>15000000</v>
       </c>
       <c r="F20" s="6" t="n">
         <v>20</v>
       </c>
       <c r="G20" s="7" t="n">
-        <v>160</v>
+        <v>200</v>
       </c>
       <c r="H20" s="7" t="n">
-        <v>16000000</v>
+        <v>20000000</v>
       </c>
       <c r="I20" s="11" t="inlineStr">
         <is>
@@ -1126,25 +1126,25 @@
         </is>
       </c>
       <c r="B21" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C21" s="4" t="n">
         <v>15</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>15000000</v>
+        <v>12000000</v>
       </c>
       <c r="F21" s="4" t="n">
         <v>15</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>15000000</v>
+        <v>12000000</v>
       </c>
       <c r="I21" s="8" t="inlineStr"/>
     </row>
@@ -1188,25 +1188,25 @@
         </is>
       </c>
       <c r="B23" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C23" s="4" t="n">
         <v>15</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>135</v>
+        <v>150</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>13500000</v>
+        <v>15000000</v>
       </c>
       <c r="F23" s="4" t="n">
         <v>15</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>135</v>
+        <v>150</v>
       </c>
       <c r="H23" s="5" t="n">
-        <v>13500000</v>
+        <v>15000000</v>
       </c>
       <c r="I23" s="8" t="inlineStr"/>
     </row>
@@ -1217,25 +1217,25 @@
         </is>
       </c>
       <c r="B24" s="9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C24" s="9" t="n">
         <v>15</v>
       </c>
       <c r="D24" s="10" t="n">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="E24" s="10" t="n">
-        <v>13500000</v>
+        <v>12000000</v>
       </c>
       <c r="F24" s="9" t="n">
         <v>15</v>
       </c>
       <c r="G24" s="10" t="n">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="H24" s="10" t="n">
-        <v>13500000</v>
+        <v>12000000</v>
       </c>
       <c r="I24" s="11" t="inlineStr">
         <is>
@@ -1250,25 +1250,25 @@
         </is>
       </c>
       <c r="B25" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>15</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>120</v>
+        <v>135</v>
       </c>
       <c r="E25" s="5" t="n">
-        <v>12000000</v>
+        <v>13500000</v>
       </c>
       <c r="F25" s="4" t="n">
         <v>15</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>120</v>
+        <v>135</v>
       </c>
       <c r="H25" s="5" t="n">
-        <v>12000000</v>
+        <v>13500000</v>
       </c>
       <c r="I25" s="8" t="inlineStr">
         <is>
@@ -1283,25 +1283,25 @@
         </is>
       </c>
       <c r="B26" s="9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C26" s="9" t="n">
         <v>15</v>
       </c>
       <c r="D26" s="10" t="n">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="E26" s="10" t="n">
-        <v>15000000</v>
+        <v>13500000</v>
       </c>
       <c r="F26" s="9" t="n">
         <v>15</v>
       </c>
       <c r="G26" s="10" t="n">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="H26" s="10" t="n">
-        <v>15000000</v>
+        <v>13500000</v>
       </c>
       <c r="I26" s="11" t="inlineStr"/>
     </row>
@@ -1345,25 +1345,25 @@
         </is>
       </c>
       <c r="B28" s="9" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C28" s="9" t="n">
         <v>15</v>
       </c>
       <c r="D28" s="10" t="n">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="E28" s="10" t="n">
-        <v>12000000</v>
+        <v>15000000</v>
       </c>
       <c r="F28" s="6" t="n">
         <v>20</v>
       </c>
       <c r="G28" s="7" t="n">
-        <v>160</v>
+        <v>200</v>
       </c>
       <c r="H28" s="7" t="n">
-        <v>16000000</v>
+        <v>20000000</v>
       </c>
       <c r="I28" s="11" t="inlineStr">
         <is>
@@ -1378,25 +1378,25 @@
         </is>
       </c>
       <c r="B29" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C29" s="4" t="n">
         <v>15</v>
       </c>
       <c r="D29" s="5" t="n">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="E29" s="5" t="n">
-        <v>15000000</v>
+        <v>12000000</v>
       </c>
       <c r="F29" s="6" t="n">
         <v>20</v>
       </c>
       <c r="G29" s="7" t="n">
-        <v>200</v>
+        <v>160</v>
       </c>
       <c r="H29" s="7" t="n">
-        <v>20000000</v>
+        <v>16000000</v>
       </c>
       <c r="I29" s="8" t="inlineStr">
         <is>
@@ -1444,25 +1444,25 @@
         </is>
       </c>
       <c r="B31" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C31" s="4" t="n">
         <v>15</v>
       </c>
       <c r="D31" s="5" t="n">
-        <v>120</v>
+        <v>135</v>
       </c>
       <c r="E31" s="5" t="n">
-        <v>12000000</v>
+        <v>13500000</v>
       </c>
       <c r="F31" s="4" t="n">
         <v>15</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>120</v>
+        <v>135</v>
       </c>
       <c r="H31" s="5" t="n">
-        <v>12000000</v>
+        <v>13500000</v>
       </c>
       <c r="I31" s="8" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
@@ -1485,10 +1485,10 @@
         </is>
       </c>
       <c r="D32" s="12" t="n">
-        <v>3510</v>
+        <v>3525</v>
       </c>
       <c r="E32" s="12" t="n">
-        <v>351000000</v>
+        <v>352500000</v>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="G32" s="12" t="n">
-        <v>3980</v>
+        <v>4005</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>398000000</v>
+        <v>400500000</v>
       </c>
       <c r="I32" s="13" t="inlineStr"/>
     </row>

--- a/docs/proposals/softbank-ultraman-caravan/SB様提示用_月別ライン供給計画_27ヶ月版.xlsx
+++ b/docs/proposals/softbank-ultraman-caravan/SB様提示用_月別ライン供給計画_27ヶ月版.xlsx
@@ -1534,7 +1534,7 @@
     <row r="38">
       <c r="A38" s="15" t="inlineStr">
         <is>
-          <t>・北関東エリアは2027年1〜3月は実施できません(4月以降は可)。ウルトラセブンは対象外です。</t>
+          <t>・関信越エリア(埼玉・茨城・群馬・栃木・山梨・長野・新潟)は2027年1〜3月は実施できません(4月以降は可)。ウルトラセブンは対象外です。</t>
         </is>
       </c>
     </row>
